--- a/data/trans_orig/P36BPD05_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD05_2023-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el número de raciones de carnes rojas, hamburguesas, salchichas o embutidos que consume al día en 2023</t>
+          <t>Población según el número de raciones de carnes rojas, hamburguesas, salchichas o embutidos que consume al día en 2023 (tasa de respuesta: 99,7%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>149479</t>
+          <t>149397</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>191310</t>
+          <t>192167</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>29,21%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>37,39%</t>
+          <t>37,55%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>188716</t>
+          <t>187773</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>225120</t>
+          <t>225695</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>29,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>348101</t>
+          <t>349701</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>405363</t>
+          <t>405013</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>27,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>32,05%</t>
+          <t>32,02%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>320399</t>
+          <t>319542</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>362230</t>
+          <t>362312</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>62,61%</t>
+          <t>62,45%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>70,79%</t>
+          <t>70,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>527850</t>
+          <t>527275</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>564254</t>
+          <t>565197</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>70,1%</t>
+          <t>70,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>74,94%</t>
+          <t>75,06%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>859316</t>
+          <t>859666</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>916578</t>
+          <t>914978</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>67,95%</t>
+          <t>67,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>72,48%</t>
+          <t>72,35%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>731848</t>
+          <t>731346</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1329957</t>
+          <t>1355578</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>32,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>58,19%</t>
+          <t>59,31%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>663267</t>
+          <t>664206</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1262543</t>
+          <t>1235118</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>29,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>56,56%</t>
+          <t>55,33%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1450472</t>
+          <t>1456681</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2295225</t>
+          <t>2245456</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>32,24%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>50,8%</t>
+          <t>49,7%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>955592</t>
+          <t>929971</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1553701</t>
+          <t>1554203</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>41,81%</t>
+          <t>40,69%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>67,98%</t>
+          <t>68,0%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>969863</t>
+          <t>997288</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1569139</t>
+          <t>1568200</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>43,44%</t>
+          <t>44,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>70,29%</t>
+          <t>70,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2222730</t>
+          <t>2272499</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3067483</t>
+          <t>3061274</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>49,2%</t>
+          <t>50,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>67,9%</t>
+          <t>67,76%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>158815</t>
+          <t>158191</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>215039</t>
+          <t>214473</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>24,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>33,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>123394</t>
+          <t>123570</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>163228</t>
+          <t>162212</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>294007</t>
+          <t>290940</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>361096</t>
+          <t>359618</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>27,53%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>431584</t>
+          <t>432150</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>487808</t>
+          <t>488432</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>66,74%</t>
+          <t>66,83%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>75,44%</t>
+          <t>75,54%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>496585</t>
+          <t>497601</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>536419</t>
+          <t>536243</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>75,26%</t>
+          <t>75,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,3%</t>
+          <t>81,27%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>945340</t>
+          <t>946818</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1012429</t>
+          <t>1015496</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>72,36%</t>
+          <t>72,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>77,5%</t>
+          <t>77,73%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1078173</t>
+          <t>1082395</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1751649</t>
+          <t>1742950</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>31,31%</t>
+          <t>31,43%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>50,86%</t>
+          <t>50,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1009756</t>
+          <t>1020672</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1648976</t>
+          <t>1657173</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>28,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>45,24%</t>
+          <t>45,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2154986</t>
+          <t>2168193</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3074942</t>
+          <t>3194276</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>30,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>43,38%</t>
+          <t>45,06%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1692232</t>
+          <t>1700931</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2365708</t>
+          <t>2361486</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>49,14%</t>
+          <t>49,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>68,69%</t>
+          <t>68,57%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1996214</t>
+          <t>1988017</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2635434</t>
+          <t>2624518</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>54,76%</t>
+          <t>54,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,3%</t>
+          <t>72,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4014129</t>
+          <t>3894795</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4934085</t>
+          <t>4920878</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>56,62%</t>
+          <t>54,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,6%</t>
+          <t>69,41%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P36BPD05_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD05_2023-Estudios-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>170848</t>
+          <t>184135</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>149397</t>
+          <t>162348</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>192167</t>
+          <t>205833</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>32,02%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>37,55%</t>
+          <t>35,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>206049</t>
+          <t>234521</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>187773</t>
+          <t>214168</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>225695</t>
+          <t>255830</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>31,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>376897</t>
+          <t>418655</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>349701</t>
+          <t>389565</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>405013</t>
+          <t>447845</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>30,02%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>27,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>32,12%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>340861</t>
+          <t>390992</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>319542</t>
+          <t>369294</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>362312</t>
+          <t>412779</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>66,61%</t>
+          <t>67,98%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>62,45%</t>
+          <t>64,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>70,8%</t>
+          <t>71,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>546921</t>
+          <t>584850</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>527275</t>
+          <t>563541</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>565197</t>
+          <t>605203</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>72,64%</t>
+          <t>71,38%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>70,03%</t>
+          <t>68,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>75,06%</t>
+          <t>73,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>887782</t>
+          <t>975842</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>859666</t>
+          <t>946652</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>914978</t>
+          <t>1004932</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>70,2%</t>
+          <t>69,98%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>67,98%</t>
+          <t>67,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>72,35%</t>
+          <t>72,06%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>511709</t>
+          <t>575127</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>511709</t>
+          <t>575127</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>511709</t>
+          <t>575127</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>752970</t>
+          <t>819371</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>752970</t>
+          <t>819371</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>752970</t>
+          <t>819371</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1264679</t>
+          <t>1394497</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1264679</t>
+          <t>1394497</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1264679</t>
+          <t>1394497</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>914433</t>
+          <t>751084</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>731346</t>
+          <t>702513</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1355578</t>
+          <t>804458</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>40,01%</t>
+          <t>33,75%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>31,57%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>59,31%</t>
+          <t>36,15%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>846511</t>
+          <t>647348</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>664206</t>
+          <t>610081</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1235118</t>
+          <t>692225</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>37,92%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>28,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>55,33%</t>
+          <t>31,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1760944</t>
+          <t>1398433</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1456681</t>
+          <t>1340819</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2245456</t>
+          <t>1466995</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>38,98%</t>
+          <t>31,85%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>30,54%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>49,7%</t>
+          <t>33,41%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1371116</t>
+          <t>1474464</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>929971</t>
+          <t>1421090</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1554203</t>
+          <t>1523035</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>59,99%</t>
+          <t>66,25%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>40,69%</t>
+          <t>63,85%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>68,0%</t>
+          <t>68,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1385895</t>
+          <t>1517911</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>997288</t>
+          <t>1473034</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1568200</t>
+          <t>1555178</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>62,08%</t>
+          <t>70,1%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>44,67%</t>
+          <t>68,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>70,25%</t>
+          <t>71,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>2757011</t>
+          <t>2992375</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2272499</t>
+          <t>2923813</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3061274</t>
+          <t>3049989</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>61,02%</t>
+          <t>68,15%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>50,3%</t>
+          <t>66,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>67,76%</t>
+          <t>69,46%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2285549</t>
+          <t>2225548</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2285549</t>
+          <t>2225548</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2285549</t>
+          <t>2225548</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2232406</t>
+          <t>2165259</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2232406</t>
+          <t>2165259</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2232406</t>
+          <t>2165259</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4517955</t>
+          <t>4390808</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4517955</t>
+          <t>4390808</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4517955</t>
+          <t>4390808</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>183429</t>
+          <t>197159</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>158191</t>
+          <t>168484</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>214473</t>
+          <t>224656</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>33,17%</t>
+          <t>31,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>141437</t>
+          <t>154960</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>123570</t>
+          <t>137025</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>162212</t>
+          <t>176345</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>324866</t>
+          <t>352119</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>290940</t>
+          <t>318068</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>359618</t>
+          <t>387337</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>26,79%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>463194</t>
+          <t>514428</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>432150</t>
+          <t>486931</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>488432</t>
+          <t>543103</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>71,63%</t>
+          <t>72,29%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>66,83%</t>
+          <t>68,43%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>75,54%</t>
+          <t>76,32%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>518376</t>
+          <t>579220</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>497601</t>
+          <t>557835</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>536243</t>
+          <t>597155</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>78,56%</t>
+          <t>78,89%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>75,42%</t>
+          <t>75,98%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,27%</t>
+          <t>81,34%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>981570</t>
+          <t>1093648</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>946818</t>
+          <t>1058430</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1015496</t>
+          <t>1127699</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>75,13%</t>
+          <t>75,64%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>72,47%</t>
+          <t>73,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>77,73%</t>
+          <t>78,0%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>659813</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>659813</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>659813</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1306436</t>
+          <t>1445767</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1306436</t>
+          <t>1445767</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1306436</t>
+          <t>1445767</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1268710</t>
+          <t>1132378</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1082395</t>
+          <t>1071769</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1742950</t>
+          <t>1197019</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>36,84%</t>
+          <t>32,24%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>30,52%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>50,61%</t>
+          <t>34,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1193997</t>
+          <t>1036829</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1020672</t>
+          <t>991245</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1657173</t>
+          <t>1087465</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>26,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>45,46%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>2462707</t>
+          <t>2169207</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2168193</t>
+          <t>2086151</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3194276</t>
+          <t>2253186</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>30,0%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>45,06%</t>
+          <t>31,16%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2175171</t>
+          <t>2379884</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1700931</t>
+          <t>2315243</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2361486</t>
+          <t>2440493</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>63,16%</t>
+          <t>67,76%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>49,39%</t>
+          <t>65,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>68,57%</t>
+          <t>69,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2451193</t>
+          <t>2681981</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1988017</t>
+          <t>2631345</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2624518</t>
+          <t>2727565</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>67,24%</t>
+          <t>72,12%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>54,54%</t>
+          <t>70,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,0%</t>
+          <t>73,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>4626364</t>
+          <t>5061865</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3894795</t>
+          <t>4977886</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4920878</t>
+          <t>5144921</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>65,26%</t>
+          <t>70,0%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>54,94%</t>
+          <t>68,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,41%</t>
+          <t>71,15%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3443881</t>
+          <t>3512262</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3443881</t>
+          <t>3512262</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3443881</t>
+          <t>3512262</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3645190</t>
+          <t>3718810</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3645190</t>
+          <t>3718810</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3645190</t>
+          <t>3718810</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7089071</t>
+          <t>7231072</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7089071</t>
+          <t>7231072</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7089071</t>
+          <t>7231072</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
